--- a/important_mails_2026-04-05.xlsx
+++ b/important_mails_2026-04-05.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -485,12 +485,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>店铺绩效类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>last7</t>
+          <t>today</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -500,21 +500,117 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
+          <t>Sun, 5 Apr 2026 13:38:25 +0000</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>Your FBA removal request is complete (pVfzD86piw)</t>
+          <t>Your payment is on the way</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr"/>
       <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai US! Your payment is on the way and will arrive within three to five days.
+On 04/05/26 13:38 PDT, we initiated a transfer to your payment method (bank account ending in 003) in the amount of $
+ 177.58.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+ Amazon sellers and Amazon Pay merchants can si</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
+Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
+Per vedere i suoi ordini ed effettuare operazioni a essi relative, come per esempio l'emissione di rimborsi, visiti Seller Central al link: http://sellercentral-europe.amazon.com. Maggiori informazioni su come gestire i prodotti, gli ordini e il suo negozio online sono disponibili nelle pagine di aiuto di Seller Central.
+Per contattarci nuovamente riguardo a questo problema utilizzi il modulo di contatto di Seller Central cliccando su questo link:
+https://sellercentral-europe.amazon.com/cu/case-dashboard/view-case?caseID=12317833332
+Se desidera ricevere aiuto da altri venditori, può visitare il nostro Forum per i venditori a questo link: https://sellercentral.amazon.it/forums/
+La preghiamo di non rispondere a questo messaggio. Questa e-mail è stata inviata da un indirizzo che non accetta posta in entrata.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA removal request is complete (pVfzD86piw)</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -540,39 +636,39 @@
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr"/>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -592,39 +688,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -641,39 +737,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -696,39 +792,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -748,39 +844,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -803,39 +899,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -853,39 +949,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -903,39 +999,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -955,39 +1051,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1005,39 +1101,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -1047,39 +1143,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -1089,39 +1185,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -1151,39 +1247,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1201,39 +1297,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1250,39 +1346,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1298,39 +1394,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -1359,39 +1455,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -1412,39 +1508,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1462,39 +1558,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1524,40 +1620,40 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1573,39 +1669,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1625,39 +1721,39 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1683,39 +1779,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1731,39 +1827,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1784,39 +1880,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1830,40 +1926,40 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1879,39 +1975,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1931,39 +2027,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -1977,39 +2073,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2029,39 +2125,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2082,39 +2178,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (uih6sNeVfd)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2134,39 +2230,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:33:22 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>View your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  We’ve submitted your quarterly tax report to the Chinese tax authority. You can now download the report for reference.
@@ -2183,39 +2279,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:38:31 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2232,39 +2328,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 14:28:40 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments UK Limited &lt;seller-notification@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on Your Selling on Amazon payment account</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
  We have charged your (Visa) credit card for 207.96 in an attempt to settle your account balance.
@@ -2279,39 +2375,39 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 15:11:44 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>Ajustement du solde négatif sur l'ensemble de vos comptes</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2335,39 +2431,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 15:16:36 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.pl&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Nieuregulowane saldo na koncie Amazon</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Witamy!
  Masz na swoim koncie nieuregulowane saldo w wysokośc PLN 30.46. Obciążymy tą kwotą kartę kredytową zarejestrowaną jako metoda płatności dla Twojego konta
@@ -2381,39 +2477,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 14:57:34 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Negatieve saldoaanpassing voor al je accounts</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2430,39 +2526,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 13:38:27 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2482,39 +2578,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:21:45 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2532,39 +2628,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 13:01:16 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2582,39 +2678,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 14:37:14 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Live Q&amp;A on customer feedback with experienced sellers</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/-ref--spc-em-na-frm-20260324/7z2bw3r/6577485148/h/BOm7kDreq_ieAJ8P9nkJWZ402nkYiTu_wgkPAn3aZYs)
 Connect with sellers experienced in customer feedback
@@ -2629,39 +2725,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:53 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2679,39 +2775,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:13:28 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -2729,39 +2825,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:51:52 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -2779,39 +2875,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 08:16:10 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2826,39 +2922,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 15:17:29 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2873,39 +2969,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 14:28:08 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-us@amazon.com" &lt;fba-3p-buyability-improvement-us@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are part of Buyability Audit team at Amazon. The Buyability program aims to identify and eliminate root causes leading to Buyability drop-off. We are contacting you to let you know that you could be missing out on sales opportunities due to the suppression of some of your ASINs.
@@ -2920,39 +3016,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 04:25:09 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -2971,40 +3067,40 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 11:52:08 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Submit UK import details by 21/05/2026 to avoid shipping
  restrictions</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
  Submit UK import details by 21/05/2026 to avoid shipping restrictions
@@ -3023,39 +3119,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 07:21:52 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Add products to Amazon.nl for Pan EU eligibility 96
  Complete Pan EU enrollment: Add NL products now
@@ -3065,39 +3161,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 21:58:00 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -3115,39 +3211,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 21:10:27 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>Action Required: Website Suppressed ASINs</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We are contacting you to let you know that you could be missing out on sales opportunities because of your incomplete listings.
@@ -3163,39 +3259,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Sat, 14 Mar 2026 17:19:26 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.com Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>Dear Weihai US,
 We have recently restricted listings for the product(s) listed below on Amazon.com.
@@ -3214,39 +3310,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 12:08:48 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3264,39 +3360,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 09:36:41 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"pc-eu-sesu-seller-compliance@amazon.com" &lt;pc-eu-sesu-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 11569978862] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【欧洲】各站点的部分【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3318,39 +3414,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 21:37:56 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"pc-us--sesu-cn-central-compliance@amazon.com" &lt;pc-us--sesu-cn-central-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 18425733131] 【需立即行动】请通过亚马逊认可的TIC服务提供商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 我们紧急通知您，您部分在【美国】的【儿童玩具】商品尚未完成合规，即将面临下架风险。为避免下架，请在截止日期之前完成以下操作，并确保TRF状态更新为【正在验证】。
@@ -3373,39 +3469,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:20 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3424,39 +3520,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3475,39 +3571,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3527,39 +3623,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -3579,39 +3675,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Actie vereist: Belangrijke informatie over je productvermeldingen
@@ -3629,39 +3725,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Rispondi ai requisiti di conformità per le tue offerte</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 Azione richiesta: Informazioni importanti sulle sue offerte
@@ -3679,39 +3775,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Hantera efterlevnadskrav för dina produktposter</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 Åtgärd krävs: Viktig information angående dina produktposter
@@ -3729,39 +3825,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -3780,39 +3876,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3827,39 +3923,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3873,40 +3969,40 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -3922,39 +4018,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -3970,39 +4066,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -4018,39 +4114,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4066,40 +4162,40 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4115,39 +4211,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4165,39 +4261,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -4213,39 +4309,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4260,39 +4356,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -4307,39 +4403,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4360,40 +4456,40 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -4408,39 +4504,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -4461,39 +4557,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4526,39 +4622,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4574,39 +4670,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4622,39 +4718,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4672,39 +4768,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4721,39 +4817,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4777,39 +4873,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4824,39 +4920,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4872,39 +4968,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -4921,40 +5017,40 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -4970,39 +5066,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -5022,39 +5118,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5070,40 +5166,40 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5119,39 +5215,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5168,39 +5264,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5219,39 +5315,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5269,39 +5365,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -5313,39 +5409,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5357,39 +5453,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5401,39 +5497,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5445,39 +5541,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5489,39 +5585,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5533,39 +5629,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5577,39 +5673,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5621,39 +5717,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5671,39 +5767,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5746,39 +5842,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5795,40 +5891,40 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5846,39 +5942,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5896,39 +5992,39 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5940,39 +6036,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5984,39 +6080,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6035,39 +6131,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6079,39 +6175,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6123,39 +6219,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6167,39 +6263,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6211,39 +6307,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6255,39 +6351,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6299,39 +6395,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6343,39 +6439,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6387,39 +6483,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6431,40 +6527,40 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6483,39 +6579,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6527,40 +6623,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6572,39 +6668,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6616,39 +6712,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6667,39 +6763,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6711,39 +6807,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6762,39 +6858,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
@@ -6806,39 +6902,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -6854,40 +6950,40 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
  disattivazione dell'offerta</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -6905,39 +7001,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Bonjour Weihai EU,
@@ -6955,39 +7051,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
 Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
@@ -7003,39 +7099,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Aborda los requisitos de cumplimiento de tus listings</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
 Toma medidas: Información importante sobre tus listings de producto
@@ -7053,39 +7149,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t>96
  尊敬的 Weihai EU：
@@ -7126,39 +7222,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -7176,40 +7272,40 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -7227,39 +7323,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -7276,39 +7372,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -7326,39 +7422,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7379,39 +7475,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7434,39 +7530,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7487,39 +7583,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7543,39 +7639,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7598,39 +7694,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E147" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F147" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7653,39 +7749,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E148" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F148" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7707,39 +7803,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E149" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F149" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7762,39 +7858,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="150">
+      <c r="A150" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C150" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D150" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E150" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F150" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G150" s="2" t="inlineStr"/>
+      <c r="H150" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7817,39 +7913,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="151">
+      <c r="A151" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C151" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D151" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E151" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F151" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G151" s="2" t="inlineStr"/>
+      <c r="H151" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7865,39 +7961,39 @@
         </is>
       </c>
     </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+    <row r="152">
+      <c r="A152" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C152" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D152" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E150" s="2" t="inlineStr">
+      <c r="E152" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F150" s="2" t="inlineStr">
+      <c r="F152" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
+      <c r="G152" s="2" t="inlineStr"/>
+      <c r="H152" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7913,40 +8009,40 @@
         </is>
       </c>
     </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="153">
+      <c r="A153" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C153" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D153" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E153" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F153" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G153" s="2" t="inlineStr"/>
+      <c r="H153" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7965,40 +8061,40 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="154">
+      <c r="A154" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C154" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D154" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E154" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F154" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G154" s="2" t="inlineStr"/>
+      <c r="H154" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8016,39 +8112,39 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="155">
+      <c r="A155" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C155" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D155" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E155" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F155" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G155" s="2" t="inlineStr"/>
+      <c r="H155" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8062,39 +8158,39 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="156">
+      <c r="A156" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C156" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D156" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E156" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F156" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G156" s="2" t="inlineStr"/>
+      <c r="H156" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8112,39 +8208,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="157">
+      <c r="A157" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C157" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D157" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E157" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F157" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G157" s="2" t="inlineStr"/>
+      <c r="H157" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8161,39 +8257,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="158">
+      <c r="A158" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C158" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D158" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E158" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F158" s="2" t="inlineStr">
         <is>
           <t>Behörighet att ändra alternativ för Premiumfrakt</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G158" s="2" t="inlineStr"/>
+      <c r="H158" s="2" t="inlineStr">
         <is>
           <t>96
 Behörighet att ändra alternativ för Premiumfrakt
@@ -8211,40 +8307,40 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="159">
+      <c r="A159" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C159" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D159" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E159" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F159" s="2" t="inlineStr">
         <is>
           <t>Premium Shipping option eligibility suspended due to program
  requirement violation</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G159" s="2" t="inlineStr"/>
+      <c r="H159" s="2" t="inlineStr">
         <is>
           <t>96
 Premium Shipping option eligibility suspended due to program requirement violation
@@ -8263,39 +8359,39 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+    <row r="160">
+      <c r="A160" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C160" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D160" s="2" t="inlineStr">
         <is>
           <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
         </is>
       </c>
-      <c r="E158" s="2" t="inlineStr">
+      <c r="E160" s="2" t="inlineStr">
         <is>
           <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F158" s="2" t="inlineStr">
+      <c r="F160" s="2" t="inlineStr">
         <is>
           <t>Répondez aux exigences de conformité pour vos mises en vente</t>
         </is>
       </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
+      <c r="G160" s="2" t="inlineStr"/>
+      <c r="H160" s="2" t="inlineStr">
         <is>
           <t>96
 Action requise : informations importantes concernant vos offres

--- a/important_mails_2026-04-05.xlsx
+++ b/important_mails_2026-04-05.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H160"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
+          <t>Sun, 5 Apr 2026 15:20:39 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
@@ -562,11 +562,70 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
+          <t>RE:[CASE 12317833332] 其他账户问题</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的卖家/供应商：您好！
+关于您 ASIN B0CSGBZG8W 购物车的问题，经过审核，我们发现该商品的价格不符合成为推荐商品的条件，因为它似乎过高。
+为了解决这个问题，建议您采取以下措施：
+- 降低商品价格以符合推荐条件，请访问"定价状况"页面   https://sellercentral-europe.amazon.com/pricing/health   ，并考虑根据提供的参考价设置商品的总价格（商品价格 + 运费）。建议设置价格在22欧元上下。
+- 如果您的 ASIN 有商品标价，请确保是最新价格。您提供的商品标价应该代表您、其他零售商或其他卖家最近售出或计划售出大量相关商品时所采用的价格。
+- 考虑启用自动定价功能，以便在亚马逊推出各种活动时，例如竞争推荐报价，能自动调整目录中 SKU 的价格，而不必在每次想要更新 SKU 的价格时都手动操作。
+- 您可以访问"管理所有库存"页面 https://sellercentral-europe.amazon.com/myinventory/inventory  ，并考虑可用的参考价。如果看不到参考价，请点击"首选项",然后在"价格"列下选择您的首选参考价并点击"保存更改"。
+有关更多信息,请参阅以下帮助页面：
+- 定价状况：https://sellercentral-europe.amazon.com/help/hub/reference/GSTH6YN3BR8XNWBW
+- 自动定价：https://sellercentral-europe.amazon.com/help/hub/reference/G201994820
+根据亚马逊商城公平定价政策，调整价格后，您的商品将有机会获得购物车。
+⭐温馨提示⭐：
+感谢您的信任与配合！如上所述，当前案件中您的疑问已按照流程处理完毕，在情况无变化的前提下，重新打开此案件通常不会改变处理结果。
+如果您有新的疑问，建议您点击下方链接创建新案例，系统将自动分配至对应团队，我们将竭诚为您服务。
+ https://sellercentral-europe.amazon.com/help/center?redirectSource=HelpHub
+欢迎向亚马逊提交反馈，从而帮助亚马逊改善您的开店体验。
+您对我们提供的支持是否满意？
+如果是，请单击此处
+https://sellercentral-europe.amazon.com/hz/case-dashboard/hmd?p=A3HNDFRW5XHZBR&amp;c=12317833332&amp;k=hy
+如果否，请单击此处
+https://sellercentral-europe.amazon.com/hz/case-dashboard/hmd?p=A3HNDFRW5XHZBR&amp;c=12317833332&amp;k=hn
+La ring</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 5 Apr 2026 09:59:13 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>Assistenza venditori Amazon &lt;merch.service05@amazon.it&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>&lt;p&gt;Grazie per aver creato un nuovo caso: -- 12317833332&lt;/p&gt;</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>La ringraziamo per aver contattato il Supporto al venditore di Amazon.
 Abbiamo aperto un caso riguardo al suo problema. Un membro del nostro team la contatterà appena possibile. Rispondiamo alla maggior parte delle e-mail entro 12 ore.
@@ -578,39 +637,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:11:54 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (pVfzD86piw)</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -636,39 +695,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 06:25:09 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (CQhO1/+c38)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -688,39 +747,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 15:38:29 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -737,39 +796,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 12:51:47 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Eco-contribution and EPR Pay on Behalf service fee charges</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -792,39 +851,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:13:23 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -844,39 +903,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 04:56:03 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>【请勿回复】
 尊敬的销售合作伙伴，
@@ -899,39 +958,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:19:17 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -949,39 +1008,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 02:18:50 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -999,39 +1058,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 21:25:34 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>Address compliance requirements for your listings</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 Action required: Important information about your product listings
@@ -1051,39 +1110,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 07:07:52 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1101,39 +1160,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:57:25 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>Recargo relacionado con combustible y gastos de logística: Logística de Amazon y Logística Multicanal en la UE</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
  A partir del 17 de abril de 2026, se aplicará un recargo por combustible y gastos de logística del 1,5 % a las tarifas de gestión logística de Logística de Amazon. En el caso de Logística Multicanal, este recargo entrará en vigor el 2 de mayo de 2026.
@@ -1143,39 +1202,39 @@
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B15" s="2" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
         <is>
           <t>Thu, 2 Apr 2026 14:01:37 +0000</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>Dopłata z tytułu kosztów paliwa i logistyki: usługi FBA i MFC w UE</t>
         </is>
       </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>96
  Od 17 kwietnia 2026 r. do opłat za realizację w programie „Realizacja przez Amazon” (FBA) zaczynamy doliczać dopłatę w wysokości 1,5% z tytułu kosztów paliwa i logistyki. W przypadku usługi „Realizacja wielokanałowa” (MCF) dopłata ta będzie miała zastosowanie od 2 maja 2026 r.
@@ -1185,39 +1244,39 @@
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
         <is>
           <t>Wed, 01 Apr 2026 07:28:21 +0000</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>Justin Bangina &lt;justin.bangina@vergleich.org&gt;</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">🏆 German quality seal for "Roaxkois Schwimmgurt für Pool" </t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>Hello from Berlin,
 My name is Justin and I am writing to you from Berlin on behalf of
@@ -1247,39 +1306,39 @@
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 03:11:45 +0000</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>Transparency Invoice/Credit note for 03/2026</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
         <is>
           <t>96
  Dear Customer,
@@ -1297,39 +1356,39 @@
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:25:14 +0000</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>规划您的亚马逊科技周促销活动</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -1346,39 +1405,39 @@
         </is>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B19" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>Tue, 31 Mar 2026 15:17:53 +0000</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>Third Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -1394,39 +1453,39 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B20" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 18:08:20 +0000</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon &lt;no-reply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>Tus límites de capacidad de Logística de Amazon para abril</t>
         </is>
       </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>96
  Tus límites de capacidad de Logística de Amazon para abril
@@ -1455,39 +1514,39 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B21" s="2" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
         <is>
           <t>Mon, 30 Mar 2026 15:23:46 +0000</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Feuerfeste Unterlage, 130 × 80cm Hitzebeständig bis 1800°F Hitzeschutzmatte, Grillmatte, Feuerschutzmatte, Fallschutzmatten Outdoor, Bodenschutzmatte, BBQ Grill Matte für Gasgrill Holzkohlegrill
@@ -1508,39 +1567,39 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B22" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Fri, 3 Apr 2026 09:46:59 +0000</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>C2S2 RXO Partner Broker fees increasing in May 2026</t>
         </is>
       </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -1558,39 +1617,39 @@
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B23" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 1 Apr 2026 00:16:39 +0000</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>View your US Q2-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q2-2026
@@ -1620,40 +1679,40 @@
         </is>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 16:14:53 +0000</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.65 in an attempt to settle your Amazon.ca seller account balance.
@@ -1669,39 +1728,39 @@
         </is>
       </c>
     </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 10:55:21 +0000</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (kpCypnMqWe)</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -1721,39 +1780,39 @@
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:27:53 +0000</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Your FBA removal request is complete (UvRxALtvwM)</t>
         </is>
       </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed and shipped your removal
@@ -1779,39 +1838,39 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 03:56:37 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1827,39 +1886,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 14:27:38 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -1880,39 +1939,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Mon, 16 Mar 2026 16:28:57 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>Reminder: Please share your feedback on MCF
 Dear Weihai US,
@@ -1926,40 +1985,40 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 16:15:06 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;seller-notification@amazon.ca&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Balance Paid on your Amazon Seller Account / Paiement du solde de
  votre compte vendeur Amazon</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon Services.
  We have charged your credit card (Visa) for CDN$ 44.03 in an attempt to settle your Amazon.ca seller account balance.
@@ -1975,39 +2034,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:16:41 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (V8b2nNxJ7Y)</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2027,39 +2086,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:36:35 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>Please share your feedback on MCF
 Dear Weihai US,
@@ -2073,39 +2132,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 16:33:48 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (FVSl6sGweZ)</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2125,39 +2184,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:16:27 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -2175,58 +2234,6 @@
  Copyright 2026 Amazon, Inc, or its affiliates. All rights reserved.
  Amazon.com, 410 Terry Avenue North, Seattle, WA 98109-5210
  SPC-USAmazon-404622472692539</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 04:02:47 +0000</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (uih6sNeVfd)</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-4201829-9256139
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-844426561416317</t>
         </is>
       </c>
     </row>
@@ -3523,7 +3530,7 @@
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3538,7 +3545,7 @@
       </c>
       <c r="D62" s="2" t="inlineStr">
         <is>
-          <t>Thu, 5 Mar 2026 21:09:14 +0000</t>
+          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
         </is>
       </c>
       <c r="E62" s="2" t="inlineStr">
@@ -3548,367 +3555,11 @@
       </c>
       <c r="F62" s="2" t="inlineStr">
         <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
+          <t>Pagamento elaborato con successo</t>
         </is>
       </c>
       <c r="G62" s="2" t="inlineStr"/>
       <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listing?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe that your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact on your account, close or delete any non-compliant listings that you</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:43 +0000</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>Address compliance requirements for your listings</t>
-        </is>
-      </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>96
-Action required: Important information about your product listings
- We are contacting you because you have listed products that require you to submit compliance documents.
- Product listings are missing required compliance documents
- Hello,
- We are contacting you because you have listed products that require you to submit compliance documents. Click on Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
- Review Compliance Requirements
- The table below contains a sample of your affected listings. Click on Review Compliance Requirements to see all of your affected listings.
- SKU ASIN Listing Status WHEUSGMH81901 B0DD7R3PPG At risk of removal
- Why is this happening?
-This requirement helps to ensure that products are compliant with local laws and safe for customers.
- How do I continue to sell the affected products?
-Click on Review Compliance Requirements to find out more information about the documents you need to provide for each product.
- Was there an error?
-If you believe that you do not</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:31 +0000</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central notifications (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>Address compliance requirements for your listings</t>
-        </is>
-      </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>96
-Action required: Important information about your product listings
- We are contacting you because you have listed products that require you to submit compliance documents.
- Product listings are missing required compliance documents
- Hello,
- We are contacting you because you have listed products that require you to submit compliance documents. Click Review Compliance Requirements below to see the list of affected products and submit the required compliance documents. If you do not submit the documents by the due date indicated for each product in this link, we may remove the affected listings.
- Review Compliance Requirements
- The table below contains a sample of your affected listings. Click Review Compliance Requirements to see all of your affected listings.
- SKU ASIN Listing Status WHEUSGMH81901 B0DD7R3PPG At risk of removal
- Why is this happening?
-This requirement helps ensure that products are compliant with local laws and safe for customers.
- How do I continue to sell the affected products?
-Click Review Compliance Requirements to find out more information about the documents you need to provide for each product.
- Was there an error?
-If you believe that you do not need to sub</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:14 +0000</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central-meldingen (niet beantwoorden)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>Vereisten voor naleving van je productvermeldingen aanpakken</t>
-        </is>
-      </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>96
-Actie vereist: Belangrijke informatie over je productvermeldingen
- We nemen contact met je op omdat je producten hebt vermeld waarvoor je nalevingsdocumenten moet indienen.
- Productvermeldingen ontbreken vereiste nalevingsdocumenten
- Hallo,
- We nemen contact met je op omdat je producten hebt vermeld waarvoor je nalevingsdocumenten moet indienen. Klik hieronder op Nalevingsvereisten bekijken om de lijst met betrokken producten te bekijken en de vereiste nalevingsdocumenten in te dienen. Als de documenten nog niet zijn ingediend op de vervaldatum die voor elk product in deze link is aangegeven, kunnen we de betreffende productvermeldingen verwijderen.
- Nalevingsvereisten bekijken
- In de onderstaande tabel zie je een voorbeeld van je betrokken productvermeldingen. Klik op Nalevingsvereisten bekijken om al je betrokken productvermeldingen weer te geven.
- SKU ASIN Status van productvermelding WHEUSGMH81901 B0DD7R3PPG Risico van verwijdering
- Waarom gebeurt dit?
-Met deze vereiste zorgen we ervoor dat producten voldoen aan de lokale wetgeving en veilig zijn voor klanten.
- Hoe kan ik de betrokken producten blijven verkopen?
-Klik op Nalevingsvereisten bekijken voor meer informatie over d</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="inlineStr">
-        <is>
-          <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>Rispondi ai requisiti di conformità per le tue offerte</t>
-        </is>
-      </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>96
-Azione richiesta: Informazioni importanti sulle sue offerte
- La contattiamo perché ha pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità.
- Le offerte dei prodotti sono prive dei documenti di conformità obbligatori
- Buongiorno,
- ti contattiamo perché hai pubblicato offerte di prodotti che richiedono l'invio di documenti di conformità. Clicca su Visualizza requisiti di conformità qui sotto per accedere all'elenco dei prodotti interessati e inviare i documenti di conformità richiesti. Se non invierai i documenti entro il termine indicato per ciascun prodotto, le offerte di tali prodotti potrebbero essere rimosse.
- Visualizza requisiti di conformità
- La tabella seguente contiene un campione delle offerte interessate. Clicca su Visualizza requisiti di conformità per accedere all'elenco completo.
- SKU ASIN Stato delle offerte WHEUSGMH81901 B0DD7R3PPG A rischio di rimozione
- Perché succede questo?
-L'aderenza ai requisiti contribuisce a garantire che i prodotti siano conformi alle leggi locali e non rappresentino un rischio per i clienti.
- Come faccio a continuare a vendere i prodotti interessati?
-Clicca su Visualizza requisiti di conformità per ottenere ma</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:05 +0000</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr">
-        <is>
-          <t>Aviseringar från Amazon Seller Central (svara inte) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F67" s="2" t="inlineStr">
-        <is>
-          <t>Hantera efterlevnadskrav för dina produktposter</t>
-        </is>
-      </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>96
-Åtgärd krävs: Viktig information angående dina produktposter
- Vi kontaktar dig eftersom du har publicerat produkter som du måste skicka in dokument om överensstämmelse för.
- Produktposterna saknar dokument om överensstämmelse
- Hej!
- Vi kontaktar dig eftersom du har publicerat produkter för vilka du måste skicka in dokument om överensstämmelse. Klicka på Granska krav på överensstämmelse nedan om du vill visa listan med berörda produkter och skicka sedan in de dokument om överensstämmelse som krävs. Om du inte skickar in dokumenten senast det angivna förfallodatumet för respektive produkt i den här länken, så kan vi komma att ta bort de berörda produktposterna.
- Visa krav på överensstämmelse
- I tabellen nedan visas en av dina berörda produktposter som exempel. Klicka på Granska krav på överensstämmelse om du vill se alla dina berörda produktposter.
- SKU ASIN Status WHEUSGMH81901 B0DD7R3PPG Riskerar borttagning
- Varför händer det här?
-Det här kravet hjälper till att säkerställa att produkterna är säkra för kunderna och överensstämmer med lokala lagar.
- Vad behöver jag göra om jag vill fortsätta att sälja de här produkterna?
-Klicka på Granska krav på överensstämmelse om du vill ha m</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:11:29 +0000</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to avoid listing deactivation</t>
-        </is>
-      </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hello Weihai EU,
- Some of your listings are at risk of deactivation due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject to these compliance requirements.
- For step-by-step instructions, see our Submit compliance documents or appeal a documentation request help page.
- To avoid further impact to your account, close or delete any non-compliant listings that you do</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 28 Mar 2026 15:19:12 +0000</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>Pagamento elaborato con successo</t>
-        </is>
-      </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -3923,39 +3574,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:18:58 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu ponownego aktywowania ofert
@@ -3969,40 +3620,40 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:09 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Invia la documentazione sulla sicurezza del prodotto per riattivare
  le offerte</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
  Invia la documentazione sulla sicurezza del prodotto per riattivare le offerte
@@ -4018,39 +3669,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:14:05 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
  Skicka in produktsäkerhetsdokumentation för att återaktivera produktposter
@@ -4066,39 +3717,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 13:10:09 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Soumettre la documentation de sécurité des produits pour réactiver les mises en vente</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
  Soumettre la documentation de sécurité des produits pour réactiver les mises en vente
@@ -4114,39 +3765,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:23:28 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para reactivar los listings</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
  Presenta la documentación sobre seguridad del producto para reactivar los listings
@@ -4162,40 +3813,40 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 12:18:15 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om productvermeldingen
  opnieuw te activeren</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Dien productveiligheidsdocumentatie in om productvermeldingen opnieuw te activeren
@@ -4211,39 +3862,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 11:10:19 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -4261,39 +3912,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 26 Mar 2026 17:28:37 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Raport podatkowy dla Chin za okres od października do grudnia 2025 r.</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Przesłaliśmy Twój kwartalny raport podatkowy chińskiemu urzędowi skarbowemu. Możesz teraz pobrać raport do wglądu.
@@ -4309,39 +3960,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Wed, 25 Mar 2026 15:00:54 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4356,39 +4007,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 10:50:35 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>借助 Climate Pledge Friendly 推动业务增长
 尊敬的卖家，
@@ -4403,39 +4054,39 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 24 Mar 2026 06:57:58 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -4456,40 +4107,40 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 18:21:26 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>Submit your Prime Day 2026 Deals on March 24, review updated fees
  and eligibility</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>96
  Get ready to make this Prime Day your best yet.
@@ -4504,39 +4155,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Mon, 23 Mar 2026 06:28:27 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>"Amazon.de" &lt;store-news@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Dein Einkaufswagen wartet</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.de/gp/cart/view.html?ref_=cor
 Alckijy Feuerfeste Unterlage | 100 * 150cm Faltbare Hitzeschutzmatte | Bodenschutzmatte | Grillmatten | Bodenmatte | Grillteppich | Funkenschutzplatte | für BBQ Grills Kaminöfen Boden Rasen usw
@@ -4557,39 +4208,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sat, 21 Mar 2026 06:12:01 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>亚马逊全球开店 &lt;info@globalselling.amazon.cn&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>【爆单预警】百亿流量即将开闸！现在备货，抢占流量C位</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家：
 						我们注意到您在店铺中有上架教育、办公类商品，特此预告您将有机会参与即将到来的全球教育采购 “超级旺季”！
@@ -4622,39 +4273,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 16:40:09 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Multi-Channel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>Second Reminder: Upcoming changes to MCF and Buy with Prime packaging
 Dear there,
@@ -4670,39 +4321,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 15:16:22 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4718,39 +4369,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 10:25:38 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>The Fulfillment by Amazon team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>Act today &amp; improve Sales on Excess Inventory</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4768,39 +4419,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 19 Mar 2026 09:02:06 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Seller News: March 2026</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services
  96
@@ -4817,39 +4468,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 17 Mar 2026 05:46:24 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>A Amazon enviou os itens vendidos</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  Processamos e enviamos seus pedidos do programa FBA - Logística da Amazon.
@@ -4873,39 +4524,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 14:55:03 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Pagamento elaborato con successo</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4920,39 +4571,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 11:03:39 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>[Toma medidas] Proporciona más información en un plazo de 45 días para evitar la desactivación de tu cuenta en virtud de los requisitos de registro a efectos fiscales en Europa</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hola, Weihai EU:
@@ -4968,39 +4619,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:19:31 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>[Wymagane działanie] Podaj dodatkowe informacje w ciągu 45 dni, aby zapobiec dezaktywacji konta z powodu niespełnienia europejskich wymagań dotyczących rejestracji jako podatnik VAT</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5017,40 +4668,40 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:50:00 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>[Azione richiesta] Fornisci informazioni entro 45 giorni ed evita
  la disattivazione dell'account per via dei requisiti di registrazione IVA</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
  Gentile Weihai EU,
@@ -5066,39 +4717,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 14:17:27 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace KSA &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>FBA removal fees will not apply in UAE and Saudi Arabia</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 Amazon UAE
@@ -5118,39 +4769,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Thu, 12 Mar 2026 11:10:46 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>¡Buenos días!
 Espero que te encuentres bien.
@@ -5166,40 +4817,40 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Wed, 11 Mar 2026 12:18:47 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;store-news@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Swimming Training Belt, 2.5-7.5M Adjustable Swimming Resistance
  Bands is still in your basket</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>https://www.amazon.co.uk/gp/cart/view.html?ref_=cor
 Schwimmgurt für Pool, Schwimmhilfe Erwachsene Pool, Schwimmgurt Pool Erwachsene, Schwimmwiderstand Gürtel mit 2.5-7.5M Einstellbare Schwimmseil für Jedes Schwimmbad Ohne Gegenstromanlage
@@ -5215,39 +4866,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 09:31:04 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;noreply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>春季促销日 2026：最后提报您促销活动的机会</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>立即规划您的促销
 尊敬的卖家：
@@ -5264,39 +4915,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 15:38:05 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 2/2026 (Votre Facture Expédié Par Amazon Amazon.ca pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5315,39 +4966,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Mon, 9 Mar 2026 11:10:45 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Worten Marketplace - Portugal y España</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>Hola Weihai EU,
 Soy Gabriel Martins, Business Developer en Worten worten.pt / worten.es , el mayor marketplace de Portugal.
@@ -5365,39 +5016,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Sat, 7 Mar 2026 01:02:00 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Credit Note for 2/2026</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Credit Note for the month of 2/2026 is now available in your Seller Central Account.
@@ -5409,39 +5060,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:28:03 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5453,39 +5104,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:16:57 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Je Creditnota Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Creditnota Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -5497,39 +5148,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 23:10:12 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnungskorrektur Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnungskorrektur Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5541,39 +5192,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 22:15:50 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -5585,39 +5236,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 21:01:28 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Amazon.pl – Faktura Realizacja przez Amazon za 2 2026</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
 Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Realizacja przez Amazon za miesiąc 2 i rok 2026.
@@ -5629,39 +5280,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:56:07 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -5673,39 +5324,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:28:14 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -5717,39 +5368,39 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:57 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
  Hola, Weihai EU:
@@ -5767,39 +5418,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:17:26 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>提交商品安全文件以避免商品被停售</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  尊敬的 Weihai EU：
@@ -5842,39 +5493,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:57 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>96
  Dzień dobry Weihai EU,
@@ -5891,40 +5542,40 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:15:27 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Dien productveiligheidsdocumentatie in om de deactivering van de
  productvermelding te voorkomen</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
  Hallo Weihai EU,
@@ -5942,39 +5593,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:12:48 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
  Hej Weihai EU!
@@ -5992,39 +5643,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:07:18 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6036,39 +5687,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:17 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E106" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F106" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Verkäufer von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Verkäufer für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6080,39 +5731,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 20:02:06 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.com.be voor 2/2026 (Votre Facture Expédié Par Amazon Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6131,39 +5782,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:35:00 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk AGL Merchant Self-Billing Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic AGL Merchant Self-Billing Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6175,39 +5826,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:32:44 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6219,39 +5870,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 19:24:20 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6263,39 +5914,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:55:05 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Rechnung Versand durch Amazon von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Rechnung Versand durch Amazon für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6307,39 +5958,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 18:24:37 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6351,39 +6002,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:58:56 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6395,39 +6046,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:48:50 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.ie Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6439,39 +6090,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 17:11:22 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Ihr Dokument Selbstfakturierung AGL von Amazon.de für 2.2026</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>Guten Tag Shen zhen shi wei hai zhong xin ke ji you xian!
 Wir möchten Sie darüber informieren, dass Ihr elektronisches Dokument Selbstfakturierung AGL für 2.2026 ab sofort in Ihrem Seller Central-Konto verfügbar ist.
@@ -6483,39 +6134,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:54:03 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Your Amazon.co.uk Fulfillment by Amazon Merchant Invoice for 2/2026</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
 We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
@@ -6527,40 +6178,40 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:44:53 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Verkoper Amazon.com.be voor 2/2026 (Votre Facture
  Vendeur Amazon.com.be pour le mois de 2/2026)</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Verkoper voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6579,39 +6230,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:38:12 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Je Factuur Fulfilled by Amazon Amazon.nl voor 2/2026</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>Beste Shen zhen shi wei hai zhong xin ke ji you xian,
 We sturen je dit bericht om je te laten weten dat je elektronische Factuur Fulfilled by Amazon voor de maand 2 2026 nu beschikbaar is in je Seller Central-account.
@@ -6623,40 +6274,40 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:28:10 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>La tua Fattura Elettronica Amazon Marketing Service Amazon.it per
  2/2026</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>Gentile Shen zhen shi wei hai zhong xin ke ji you xian,
 Ti informiamo che la tua Fattura Elettronica Amazon Marketing Service per il mese di 2/2026 è ora disponibile sul tuo account di Seller Central.
@@ -6668,39 +6319,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 6 Mar 2026 16:09:11 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>donotreply@amazon.com</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Din Faktura Säljare Amazon.se för 2/2026</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
 Vi skriver för att informera dig om att din elektroniska Faktura Säljare för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
@@ -6712,749 +6363,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 15:32:33 +0000</t>
-        </is>
-      </c>
-      <c r="E128" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F128" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.sa Fulfillment by Amazon Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاصة بك لشهر 2/2026)</t>
-        </is>
-      </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.sa
- عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
-نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) لتاجر Fulfilment by Amazon الخاص بك لشهر 2/2026 متاح الآن في حساب Seller Central الخاص بك.
-للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
-في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
-إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
- مع أطيب التحيات،
-Amazon.sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 15:13:19 +0000</t>
-        </is>
-      </c>
-      <c r="E129" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F129" s="2" t="inlineStr">
-        <is>
-          <t>Din Faktura Fraktas Av Amazon Amazon.se för 2/2026</t>
-        </is>
-      </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
-        <is>
-          <t>Hej Shen zhen shi wei hai zhong xin ke ji you xian!
-Vi skriver för att informera dig om att din elektroniska Faktura Fraktas Av Amazon för månaden 2/2026 nu finns tillgänglig på ditt Seller Central-konto.
-För att komma åt ditt fakturagår du till ditt Seller Central-konto &gt; Rapporter &gt; Bibliotek för skattedokument &gt; Skattefakturor för säljaravgifter.
-På ditt Seller Central-konto kan du se, ladda ner eller skriva ut ditt faktura.
-Om du har några frågor, kontakta säljarsupport.
-Vänliga hälsningar,
-Amazon.se</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 14:56:47 +0000</t>
-        </is>
-      </c>
-      <c r="E130" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F130" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.sa Merchant Invoice for 2/2026 (Amazon.sa فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاصة بك لشهر 2/2026)</t>
-        </is>
-      </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
-        <is>
-          <t>Dear Shen zhen shi wei hai zhong xin ke ji you xian,
-We are writing to inform you that your electronic Merchant Invoice for the month of 2/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Seller Central Account &gt; Reports &gt; Tax Document Library &gt; Seller Fee Tax Invoices.
-In your Seller Central account, you will be able to view, download or print your invoice.
-If you have any questions, please contact Seller Support.
-Best regards,
-Amazon.sa
- عزيزي Shen zhen shi wei hai zhong xin ke ji you xian،
-نراسلك لإبلاغك بأن فاتورة ضريبة القيمة المضافة (VAT) الخاصة بالتاجر الخاص بك لشهر 2/2026 متاح الآن في حساب Seller Central الخاص بك.
-للوصول إلى فاتورة الخاص بك، انتقل إلى حساب Seller Central الخاص بك &gt; التقارير &gt; مكتبة المستندات الضريبية &gt; فواتير ضريبة رسم البائع.
-في حساب Seller Central الخاص بك، ستتمكن من عرض {documentType}$ الخاص بك أو تنزيله أو طباعته.
-إذا كانت لديك أي أسئلة، فالمرجو التواصل مع دعم البائع.
- مع أطيب التحيات،
-Amazon.sa</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 14:29:22 +0000</t>
-        </is>
-      </c>
-      <c r="E131" s="2" t="inlineStr">
-        <is>
-          <t>donotreply@amazon.com</t>
-        </is>
-      </c>
-      <c r="F131" s="2" t="inlineStr">
-        <is>
-          <t>Amazon.pl – Faktura Sprzedawcy za 2 2026</t>
-        </is>
-      </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
-        <is>
-          <t>Cześć Shen zhen shi wei hai zhong xin ke ji you xian,
-Pragniemy poinformować, że ten elektroniczny dokument jest już dostępny na Twoim koncie Seller Central: Faktura Sprzedawcy za miesiąc 2 i rok 2026.
-Aby uzyskać dostęp do tego dokumentu typu faktura, przejdź na konto Seller Central &gt; Raporty &gt; Dokumenty podatkowe &gt; Faktury podatkowe z tytułu opłat od sprzedawcy.
-Na koncie Seller Central możesz wyświetlić, pobrać i wydrukować taki dokument (faktura).
-Jeśli masz jakieś pytania, skontaktuj się z działem pomocy dla sprzedawców.
-Pozdrawiamy,
-Amazon.pl</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 11:10:20 +0000</t>
-        </is>
-      </c>
-      <c r="E132" s="2" t="inlineStr">
-        <is>
-          <t>Gabriel Martins &lt;notifications@insgly.net&gt;</t>
-        </is>
-      </c>
-      <c r="F132" s="2" t="inlineStr">
-        <is>
-          <t>Worten Marketplace - Portugal y España</t>
-        </is>
-      </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
-        <is>
-          <t>¡Buenos días!
-Espero que te encuentres bien.
-Mi nombre es Gabriel Martins y soy Business Developer en WORTEN Portugal y España, parte de Sonae, uno de los más grandes grupos empresariales en Portugal.
-Te envío este mensaje porque nos gustaría hacer una colaboración entre Weihai EU y el Marketplace de Worten.
-Sobre Worten.
-Somos líderes en el mercado portugués, con 200 tiendas alcanzamos más de 1.2 billones de euros en ventas, de los cuales el 20% vienen del online.
-En Portugal, Worten.pt es el sitio de comercio electrónico más visitado y con mejor desempeño, recibimos más visitas que los principales marketplaces del mundo, los que consideramos nuestra competencia. En compras online, el sitio web de Worten tiene el mayor tráfico de Portugal, más de 10 millones de visitas al mes.
-Es en www.worten.pt y www.worten.es donde puedes mirar nuestro Marketplace.
-Con más de 30 categorías, el Marketplace de Worten quiere ser la plataforma donde los clientes pueden encontrar todo lo que necesitan.
-Con la gran demanda que sentimos, tenemos la oportunidad de aumentar nuestra gama de productos, ¡y trabajar con las mejores empresas es nuestra prioridad !
-Worten Marketplace tiene una estrategia B2C,</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 21:11:42 +0000</t>
-        </is>
-      </c>
-      <c r="E133" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F133" s="2" t="inlineStr">
-        <is>
-          <t>Invia la documentazione sulla sicurezza del prodotto per evitare la
- disattivazione dell'offerta</t>
-        </is>
-      </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
-        <is>
-          <t>96
- Gentile Weihai EU,
- Alcune delle tue offerte sono a rischio di disattivazione perché i relativi prodotti non soddisfano i requisiti obbligatori sulla conformità. Rivedi i dettagli e i passi successivi riportati di seguito. Puoi visualizzare le offerte interessate in fondo a questa e-mail.
- Ciò a cosa è dovuto?
- Abbiamo intrapreso questo provvedimento in quanto i tuoi prodotti non dispongono delle informazioni obbligatorie sulla conformità. Consulta la pagina di aiuto Sicurezza e conformità dei prodotti per informazioni sulle leggi, le normative e le politiche di Amazon applicabili.
- La tabella alla fine di questa e-mail contiene i requisiti di conformità specifici per i prodotti.
- Come faccio a riattivare le mie offerte?
- Per fornire le informazioni di conformità richieste, vai alla pagina Stato dell'account per individuare le richieste di conformità dei prodotti:
--
- Se disponi della documentazione richiesta, segui le istruzioni per inviare i documenti di conformità.
--
- Se ritieni che i tuoi prodotti siano esenti da questi requisiti, invia la documentazione che dimostra il motivo per cui non sono soggetti a questi requisiti di conformità.
- Per istruzioni dettagliate, consulta l</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 21:08:11 +0000</t>
-        </is>
-      </c>
-      <c r="E134" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F134" s="2" t="inlineStr">
-        <is>
-          <t>Soumettre la documentation de sécurité des produits pour éviter la désactivation des mises en vente</t>
-        </is>
-      </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
-        <is>
-          <t>96
- Bonjour Weihai EU,
- Certaines de vos mises en vente risquent d’être désactivées, car vos produits ne respectent pas les exigences de conformité obligatoires. Consultez les détails et les étapes suivantes ci-dessous. Les produits mis en vente concernés figurent à la fin de cet e-mail.
- Pourquoi cela se produit-il ?
- Nous prenons cette mesure, car ces produits ne présentent pas les informations de conformité obligatoires. Consultez notre page d’aide Sécurité et conformité des produits pour obtenir des informations sur les lois, réglementations et politiques Amazon applicables.
- Le tableau situé à la fin de cet e-mail présente les exigences de conformité spécifiques aux produits.
- Comment réactiver mes produits mis en vente ?
- Pour fournir les informations de conformité requises, accédez à la page État du compte et localisez les demandes de conformité des produits :
--
- Si vous disposez des documents requis, suivez les instructions pour soumettre vos documents de conformité.
--
- Si vous pensez que vos produits sont exemptés de ces exigences, soumettez des pièces justificatives prouvant les raisons pour lesquelles ils ne sont pas soumis à ces exigences de conformité.
- Pour des instru</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:32 +0000</t>
-        </is>
-      </c>
-      <c r="E135" s="2" t="inlineStr">
-        <is>
-          <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F135" s="2" t="inlineStr">
-        <is>
-          <t>Spełnij wymogi zgodności dotyczące Twoich ofert</t>
-        </is>
-      </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
-        <is>
-          <t>96
-Wymagane działanie: Ważna informacja dotycząca Twoich ofert produktów
- kontaktujemy się z Tobą, ponieważ wystawiasz produkty, dla których niezbędne jest złożenie dokumentów potwierdzających zgodność z wymogami.
- Do ofert produktów brakuje obowiązkowych dokumentów dotyczących zgodności z wymogami
- Dzień dobry,
- kontaktujemy się z Tobą, ponieważ wystawiasz produkty, dla których niezbędne jest przedłożenie dokumentów potwierdzających zgodność z wymogami. Kliknij opcję „Wyświetl wymagania dotyczące zgodności z wymogami” poniżej, aby wyświetlić listę produktów, których dotyczy problem, i przesłać wymagane dokumenty potwierdzające zgodność z wymogami. Jeśli nie prześlesz dokumentów w terminie wskazanym dla każdego produktu na tej stronie, możemy usunąć oferty, których dotyczy problem.
- Wyświetl wymagania dotyczące zgodności z wymogami
- Poniższa tabela zawiera przykłady ofert, których dotyczy problem. Kliknij pozycję „Wyświetl wymagania dotyczące zgodności z wymogami”, aby zobaczyć wszystkie oferty, których dotyczy problem.
- SKU ASIN Status oferty WHEUSGMH81901 B0DD7R3PPG Zagrożone usunięciem
- Skąd wynikła ta sytuacja?
-Wymóg ten pomaga zagwarantować, że produkty są zgodne z miejscowymi</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:29 +0000</t>
-        </is>
-      </c>
-      <c r="E136" s="2" t="inlineStr">
-        <is>
-          <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F136" s="2" t="inlineStr">
-        <is>
-          <t>Aborda los requisitos de cumplimiento de tus listings</t>
-        </is>
-      </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
-        <is>
-          <t>96
-Toma medidas: Información importante sobre tus listings de producto
- Nos ponemos en contacto contigo porque has publicado productos que requieren que aportes documentación sobre cumplimiento.
- Listings de producto a los que les falta la documentación sobre cumplimiento solicitada
- Hola:
- Nos ponemos en contacto contigo porque has publicado productos que requieren que aportes documentación sobre cumplimiento. Haz clic en "Revisar requisitos de cumplimiento" a continuación para ver la lista de productos en cuestión y enviar la documentación sobre cumplimiento solicitada. Si no envías la documentación dentro del plazo indicado para cada producto en este enlace, es posible que eliminemos los listings afectados.
- Revisar requisitos de cumplimiento
- La tabla siguiente contiene una muestra de los listings afectados. Haz clic en "Revisar requisitos de cumplimiento" para ver todos los listings afectados.
- SKU ASIN Estado del listing WHEUSGMH81901 B0DD7R3PPG En riesgo de retirada
- ¿A qué se debe esto?
-Con este requisito nos aseguramos de que los productos cumplan con la legislación local y de que sean seguros para los clientes.
- ¿Cómo puedo seguir vendiendo los productos afectados?
-Haz cl</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:16:47 +0000</t>
-        </is>
-      </c>
-      <c r="E137" s="2" t="inlineStr">
-        <is>
-          <t>亚马逊开店服务 &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F137" s="2" t="inlineStr">
-        <is>
-          <t>提交商品安全文件以避免商品被停售</t>
-        </is>
-      </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
-        <is>
-          <t>96
- 尊敬的 Weihai EU：
-您好！
- 您的部分商品因缺少必要的商品合规信息而面临被停售的风险。查看下面的详细信息和后续步骤。受影响的商品显示在此电子邮件的末尾。
- 为什么会发生这种情况？
- 我们之所以采取此措施，是因为这些商品缺少必要的合规信息。请查看我们的 商品安全与合规 帮助页面，了解有关适用法律法规和亚马逊政策的信息。
- 此电子邮件末尾的表格提供了特定于商品的合规性要求。
- 如何重新启售商品？
- 要提供所需的合规信息，请前往 账户状况 页面并找到商品合规性请求：
--
- 如果您有所需的文件，请按照相关说明提交您的合规文件。
--
- 如果您认为您的商品无需遵守这些要求，请提交相关文件，说明它们为何不受这些合规要求的约束。
- 有关分步操作说明，请参阅 提交合规文件或对文件请求提出申诉 帮助页面。
- 为避免进一步影响您的账户，请停售或删除您不打算销售或申诉的任何不合规商品。
- 如果我未执行上述操作，会怎么样？
- 如果您未在“账户状况”页面显示的截止日期之前提供所需的合规信息，我们可能会停售受影响的商品。
- 我们愿意随时为您提供帮助。
- 有关更多信息，请观看卖家大学中的 安全与合规简介 视频
- 如果您有其他问题，请在您的 账户状况 控制面板上提交请求。
- 亚马逊商品安全与合规性
- 受影响的商品
- 详情
- Roaxkois Töpferscheibe, Mini-Töpferscheibe für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Diamant Aufkleber
- ASIN： B0DC9Y9JQJ
- 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的法律、法规、标准和亚马逊政策。
-要销售儿童玩具，您必须满足 儿童玩具帮助页面 上列出的要求，并与我们的合作伙伴第三方测试、检验和认证 (TIC) 服务提供商合作，验证您的商品符合这些要求。
-儿童玩具是指供14岁或以下儿童在学习或玩耍时使用的商品。
-亚马逊根据以下标准来确定商品是否为“儿童玩具”：
-商品包装上的年龄分级标明该玩具专供 14 岁或以下儿童使用。
-产品的包装、展示、促销或广告显示该产品适合 14 岁或以下儿童使用。
-消费者通常认为该商品供 14 岁或以下儿童使用。
-有关合规要求、如何与 TIC 服务提供商合作的更多信息，或者要观看有关本政策涵盖的儿童玩具的视频，请访问 儿童玩具帮助页面 。
- Roaxkois Töpferscheibe, Mini-Töpferscheibe für Kinder, Töpferset für Zuhause mit ton lufttrocknend, Diamant Aufkleber
- ASIN： B0DC9Y9JQJ
- 亚马逊要求您证明自己在亚马逊德国站上架的儿童玩具符合适用的</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:16:22 +0000</t>
-        </is>
-      </c>
-      <c r="E138" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F138" s="2" t="inlineStr">
-        <is>
-          <t>Presenta la documentación sobre seguridad del producto para evitar la desactivación de los listings</t>
-        </is>
-      </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hola, Weihai EU:
- Algunos de tus listings están en riesgo de desactivación debido a que tus productos no cumplen los requisitos obligatorios. Revisa a continuación los detalles y siguientes pasos. Los listings afectados aparecen al final de este correo electrónico.
- ¿A qué se debe esto?
- Tomamos esta medida porque a estos productos les falta información de cumplimiento normativo obligatoria. Para más información sobre las leyes, normativas y políticas de Amazon aplicables, consulta Cumplimiento y seguridad de los productos .
- En la tabla que aparece al final de este correo electrónico se proporcionan los requisitos de cumplimiento normativo específicos del producto.
- ¿Cómo puedo reactivar mis listings?
- Para proporcionar la información de cumplimiento normativo obligatoria, ve a la página Estado de la cuenta y localiza las solicitudes de cumplimiento normativo del producto:
--
- Si dispones de la documentación obligatoria, sigue las instrucciones para presentar los documentos de cumplimiento normativo.
--
- Si crees que tus productos están exentos de estos requisitos, presenta documentación que demuestre por qué no están sujetos a estos requisitos de cumplimiento normativo.
- Para v</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:12:51 +0000</t>
-        </is>
-      </c>
-      <c r="E139" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F139" s="2" t="inlineStr">
-        <is>
-          <t>Dien productveiligheidsdocumentatie in om de deactivering van de
- productvermelding te voorkomen</t>
-        </is>
-      </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hallo Weihai EU,
- Enkele van je productvermeldingen lopen het risico op deactivering omdat er verplichte nalevingsvereisten voor je producten ontbreken. Bekijk de gegevens en de stappen hieronder. De betreffende productvermeldingen worden aan het einde van deze e-mail weergegeven.
- Waarom gebeurt dit?
- We hebben deze actie ondernomen omdat voor deze producten verplichte nalevingsinformatie ontbreekt. Raadpleeg onze hulp-pagina Productveiligheid en -conformiteit voor informatie over de toepasselijke wet- en regelgeving en het Amazon-beleid.
- De tabel aan het einde van deze e-mail bevat productspecifieke nalevingsvereisten.
- Hoe activeer ik mijn productvermeldingen opnieuw?
- Als je de vereiste nalevingsgegevens wilt verstrekken, ga je naar de pagina Accountstatus en zoek je de aanvragen voor productconformiteit:
--
- Als je over de vereiste documentatie beschikt, volg je de instructies om je nalevingsdocumenten in te dienen.
--
- Als je van mening bent dat je producten zijn vrijgesteld van deze vereisten, dien dan documentatie in waaruit blijkt wat de reden is dat ze niet aan deze nalevingsvereisten zijn onderworpen.
- Raadpleeg voor stapsgewijze instructies onze hulp-pagina Documente</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:11:28 +0000</t>
-        </is>
-      </c>
-      <c r="E140" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F140" s="2" t="inlineStr">
-        <is>
-          <t>Przesyłanie dokumentacji dotyczącej bezpieczeństwa produktu w celu niedopuszczenia do dezaktywacji oferty</t>
-        </is>
-      </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dzień dobry Weihai EU,
- niektóre z Twoich ofert są zagrożone dezaktywacją z powodu niespełnienia obowiązków dotyczących zgodności wystawianych przez Ciebie produktów z wymogami. Poniżej znajdziesz szczegółowe informacje oraz dalsze instrukcje. Oferty produktów, których dotyczy problem, wskazano na końcu niniejszej wiadomości e-mail.
- Dlaczego tak się stało?
- Podjęliśmy to działanie, ponieważ w przypadku tych produktów nie dostarczono obowiązkowych informacji dotyczących zgodności z wymogami. Więcej informacji na temat mających zastosowanie przepisów ustawowych i wykonawczych oraz zasad Amazon znajdziesz na stronie Bezpieczeństwo i zgodność produktu z wymogami .
- Informacje na temat wymogów dotyczących zgodności dla poszczególnych produktów znajdziesz w tabeli na końcu tej wiadomości e-mail.
- Jak mogę ponownie aktywować oferty?
- Aby dostarczyć niezbędne informacje dotyczące zgodności z wymogami, przejdź do panelu Kondycja konta i znajdź żądania dotyczące zgodności produktu z wymogami:
--
- Jeśli dysponujesz wymaganymi dokumentami zgodności, postępuj zgodnie z instrukcjami, aby je przesłać.
--
- Jeśli uważasz, że Twoje produkty są zwolnione z wymogów dotyczących zgodności, prześlij d</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:09:31 +0000</t>
-        </is>
-      </c>
-      <c r="E141" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F141" s="2" t="inlineStr">
-        <is>
-          <t>Skicka in produktsäkerhetsdokumentation för att undvika att produktposterna inaktiveras</t>
-        </is>
-      </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
-        <is>
-          <t>96
- Hej Weihai EU!
- Vissa av dina produktposter riskerar att inaktiveras på grund av att det saknas obligatorisk information om överensstämmelse för produkterna. Granska informationen och följande steg nedan. De berörda produktposterna visas i slutet av det här e-postmeddelandet.
- Varför händer det här?
- Vi vidtar den här åtgärden eftersom det saknas obligatorisk information om överensstämmelse för de här produkterna. Läs vår hjälpsida för Produktsäkerhet och -överensstämmelse för information om tillämpliga lagar, förordningar och Amazons policyer.
- Tabellen i slutet av detta e-postmeddelande innehåller produktspecifika krav för överensstämmelse.
- Hur återaktiverar jag mina produktposter?
- Om du vill tillhandahålla den begärda överensstämmelseinformationen går du till sidan Kontostatus och letar upp begäranden om produktöverensstämmelse:
--
- Om du har den obligatoriska dokumentationen ska du skicka in dina överensstämmelsedokument enligt instruktionerna.
--
- Om du tror att dina produkter är undantagna från dessa krav skickar du in dokumentation som visar varför de inte omfattas av dessa överensstämmelsekrav.
- Du hittar stegvisa instruktioner på vår hjälpsida om Skicka in intyg om öve</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:57:24 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-09</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7475,39 +6416,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 09:55:39 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7530,39 +6471,39 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:45:50 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-04-02</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7583,39 +6524,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 10:04:22 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7639,39 +6580,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Fri, 20 Mar 2026 09:25:34 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7694,39 +6635,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:45:45 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -7749,39 +6690,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Fri, 13 Mar 2026 10:21:22 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-03-26</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -7803,149 +6744,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 13:58:29 +0000</t>
-        </is>
-      </c>
-      <c r="E149" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F149" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- V8b2nNxJ7Y
- Unsellable Products:
-- FNSKU: B0FD8RGZX3 Quantity: 1
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B150" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C150" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D150" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 13:29:25 +0000</t>
-        </is>
-      </c>
-      <c r="E150" s="2" t="inlineStr">
-        <is>
-          <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F150" s="2" t="inlineStr">
-        <is>
-          <t>Disposal order created for unsellable FBA inventory</t>
-        </is>
-      </c>
-      <c r="G150" s="2" t="inlineStr"/>
-      <c r="H150" s="2" t="inlineStr">
-        <is>
-          <t>96
-Automated Removals of Unfulfillable Inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Final notice: Disposal order for your unfulfillable FBA inventory
- Hello,
-You have unfulfillable inventory that has been in a fulfilment centre for more than 14 days. We have created a disposal order for these items.
- Why is this happening?
-This action is required because these unfulfillable items have remained in our fulfilment centres for more than 14 days after notification. According to our FBA Required Removals policy, cancelling a required removal order is not permitted. To learn more, visit our FBA Required Removals policy .
- Removal order ID:
-- FVSl6sGweZ
- Unsellable Products:
-- FNSKU: X002A05YW5 Quantity: 2
- For more information about the disposal order process, see Remove inventory from a fulfilment centre .
- To monitor your unfulfillable inventory, see the Manage FBA Inventory for total unsellable quantities or the Recommended Removal report for unsellable and aged inventory details.
- The Fulfilment by Amazon Team
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferen</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B151" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C151" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Fri, 27 Mar 2026 18:36:24 +0000</t>
         </is>
       </c>
-      <c r="E151" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F151" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G151" s="2" t="inlineStr"/>
-      <c r="H151" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -7961,39 +6792,39 @@
         </is>
       </c>
     </row>
-    <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B152" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C152" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Sun, 22 Mar 2026 03:22:21 +0000</t>
         </is>
       </c>
-      <c r="E152" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>"fba-3p-buyability-improvement-ca@amazon.com" &lt;fba-3p-buyability-improvement-ca@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F152" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>[Action Required] – Update Inventory -FBA</t>
         </is>
       </c>
-      <c r="G152" s="2" t="inlineStr"/>
-      <c r="H152" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 This is an email regarding FBA Offers for your Amazon Seller account. We are contacting you to let you know that you could be missing out on sales opportunities because of low/missing inventory for your ASIN offers in the attached sheet.
@@ -8009,40 +6840,40 @@
         </is>
       </c>
     </row>
-    <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B153" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C153" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D153" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 10:33:36 +0000</t>
         </is>
       </c>
-      <c r="E153" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F153" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>[Action Required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G153" s="2" t="inlineStr"/>
-      <c r="H153" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8061,40 +6892,40 @@
         </is>
       </c>
     </row>
-    <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B154" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C154" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D154" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Sun, 15 Mar 2026 09:34:06 +0000</t>
         </is>
       </c>
-      <c r="E154" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F154" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>[Action required] Provide additional information within 45 days to
  avoid account deactivation under European VAT registration requirements</t>
         </is>
       </c>
-      <c r="G154" s="2" t="inlineStr"/>
-      <c r="H154" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -8112,39 +6943,39 @@
         </is>
       </c>
     </row>
-    <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B155" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C155" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D155" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 17:09:21 +0000</t>
         </is>
       </c>
-      <c r="E155" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F155" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Envie os documentos de conformidade do produto para evitar a remoção da oferta</t>
         </is>
       </c>
-      <c r="G155" s="2" t="inlineStr"/>
-      <c r="H155" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t>96
  Envie os documentos de conformidade do produto para evitar a remoção da oferta
@@ -8158,39 +6989,39 @@
         </is>
       </c>
     </row>
-    <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B156" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C156" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D156" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Tue, 10 Mar 2026 12:07:27 +0000</t>
         </is>
       </c>
-      <c r="E156" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Notificações do Seller Central da Amazon (não responder) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F156" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Atenda aos requisitos de conformidade em ofertas</t>
         </is>
       </c>
-      <c r="G156" s="2" t="inlineStr"/>
-      <c r="H156" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
 Ação necessária: Informações importantes sobre suas ofertas
@@ -8208,39 +7039,39 @@
         </is>
       </c>
     </row>
-    <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B157" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C157" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D157" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Sun, 8 Mar 2026 12:42:53 +0000</t>
         </is>
       </c>
-      <c r="E157" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.nl&gt;</t>
         </is>
       </c>
-      <c r="F157" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Wijziging in geschiktheid voor opties voor premiumverzending</t>
         </is>
       </c>
-      <c r="G157" s="2" t="inlineStr"/>
-      <c r="H157" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
 Wijziging in geschiktheid voor opties voor premiumverzending
@@ -8257,156 +7088,6 @@
         </is>
       </c>
     </row>
-    <row r="158">
-      <c r="A158" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B158" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C158" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D158" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 12:16:06 +0000</t>
-        </is>
-      </c>
-      <c r="E158" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.se&gt;</t>
-        </is>
-      </c>
-      <c r="F158" s="2" t="inlineStr">
-        <is>
-          <t>Behörighet att ändra alternativ för Premiumfrakt</t>
-        </is>
-      </c>
-      <c r="G158" s="2" t="inlineStr"/>
-      <c r="H158" s="2" t="inlineStr">
-        <is>
-          <t>96
-Behörighet att ändra alternativ för Premiumfrakt
-Weihai EU,
-Du är för närvarande inte berättigad att erbjuda Premiumfrakt-alternativ för dina beställningar levererade av säljare. Din status har ändrats eftersom vi har märkt att en eller flera av dina resultatmätningar har sjunkit under gränsen för programkraven.
-Du kan granska dina resultatmätningar med widgeten Berättigande för premiumfrakt . För att återställa behörigheten för alternativen för Premiumfrakt skickar du in en handlingsplan genom att svara på det här e-postmeddelandet eller skriva till op-pso-vtr-appeals@amazon.se .
-För att kunna erbjuda alternativ för Premiumfrakt måste säljare:
-- Ha sålt på Amazon i 90 dagar eller mer
-- Skickat tio eller fler beställningar de senaste 30 dagarna
-- Upprätthålla en leveranshastighet på 97 % eller högre för alla beställningar med alternativ för beställningar med Premiumfrakt
-- Upprätthålla en giltig spårningsfrekvens på 100 % för alla beställningar med Premiumfrakt
-- Upprätthålla en annulleringsgrad på 0,5 % eller mindre för alla beställningar med Premiumfrakt
-Fraktas från Amazon-beställningar (FBA) påverkas inte av denna statusändring.
- Observera : Skicka alla öppna beställningar m</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B159" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C159" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D159" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 6 Mar 2026 05:10:16 +0000</t>
-        </is>
-      </c>
-      <c r="E159" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Marketplace &lt;op-pso-vtr-appeals@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F159" s="2" t="inlineStr">
-        <is>
-          <t>Premium Shipping option eligibility suspended due to program
- requirement violation</t>
-        </is>
-      </c>
-      <c r="G159" s="2" t="inlineStr"/>
-      <c r="H159" s="2" t="inlineStr">
-        <is>
-          <t>96
-Premium Shipping option eligibility suspended due to program requirement violation
-Weihai EU,
-You are currently not eligible to offer Premium Shipping options for your seller-fulfilled orders. Your status has changed because we noticed that one or more of your performance metrics has fallen below the program requirements.
-You can review your performance metrics using the Premium Shipping Eligibility widget . To restore eligibility for Premium Shipping Options, please submit a Plan of Action by replying to this email or writing to op-pso-vtr-appeals@amazon.com .
-To offer Premium Shipping options, sellers are required to:
-- Have sold on Amazon for 90 days or more
-- Ship ten or more orders in the last 30 days
-- Maintain an on-time delivery rate of 97% or greater for all Premium Shipping option orders
-- Maintain a valid tracking rate of 100% for all Premium Shipping option orders
-- Maintain a cancellation rate of 0.5% or less for all Premium Shipping option orders
-Fulfillment by Amazon (FBA) orders are not affected by this status change.
- Note : Please ship any open Premium Shipping option orders with the ship option selected when the order was placed.
-Thank you for selling on Amazo</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B160" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C160" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D160" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 5 Mar 2026 20:28:12 +0000</t>
-        </is>
-      </c>
-      <c r="E160" s="2" t="inlineStr">
-        <is>
-          <t>Notifications Amazon Seller Central (Ne pas répondre) &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F160" s="2" t="inlineStr">
-        <is>
-          <t>Répondez aux exigences de conformité pour vos mises en vente</t>
-        </is>
-      </c>
-      <c r="G160" s="2" t="inlineStr"/>
-      <c r="H160" s="2" t="inlineStr">
-        <is>
-          <t>96
-Action requise : informations importantes concernant vos offres
- Nous vous contactons car vous avez répertorié des produits qui nécessitent que vous soumettiez des documents de conformité.
- Vos produits mis en vente ne disposent pas des documents de conformité requis
- Bonjour,
- Nous vous contactons car vous avez mis en vente des produits pour lesquels des documents de conformité sont requis. Cliquez sur Afficher les exigences de conformité ci-dessous pour consulter la liste des produits concernés et soumettre les documents de conformité nécessaires. Si vous ne soumettez pas ces documents avant la date limite indiquée pour chaque produit dans ce lien, nous pourrions supprimer les mises en vente concernées.
- Afficher les exigences de conformité
- Le tableau ci-dessous présente un échantillon de vos produits mis en vente concernés. Cliquez sur Afficher les exigences de conformité pour consulter l’ensemble de vos mises en vente concernées.
- SKU ASIN État de la mise en vente WHEUSGMH81901 B0DD7R3PPG Présentant un risque de prélèvement
- Pourquoi cela se produit-il ?
-Cette exigence nous aide à garantir que les produits respectent la législation locale et ne présentent pas de danger pour</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
